--- a/hira_material_automation/output/monthly/202601_202608__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__all_suture_anchor__040021__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T22:16:32</t>
+          <t>2026-08-14T21:28:30</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>412ebf278230823cfe8a8662076863867e2de7d9a659ceff732a145e6b6db514</t>
+          <t>67e8e3b091dd26d8dad6496ae2efb3a83ca22ef7656a0433483a6767055df09e</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202608__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__all_suture_anchor__040021__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T21:28:30</t>
+          <t>2026-08-24T21:33:40</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>67e8e3b091dd26d8dad6496ae2efb3a83ca22ef7656a0433483a6767055df09e</t>
+          <t>521dffc4bf10f595df28758aed51a61565b14995f62a1e2ecd949b0646f25049</t>
         </is>
       </c>
     </row>
